--- a/ig/DM-FEVRIER-2026/ValueSet-JDV-J129-CategorieEtablissement-RASS.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-JDV-J129-CategorieEtablissement-RASS.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -348,7 +348,7 @@
     <t>166</t>
   </si>
   <si>
-    <t>Etablissement d'Accueil Mère-Enfant</t>
+    <t>Centre Parents-Enfants de moins de 3 ans</t>
   </si>
   <si>
     <t>167</t>
@@ -924,7 +924,7 @@
     <t>286</t>
   </si>
   <si>
-    <t>Club Equipe de Prévention</t>
+    <t>Service de prévention spécialisée</t>
   </si>
   <si>
     <t>289</t>

--- a/ig/DM-FEVRIER-2026/ValueSet-JDV-J129-CategorieEtablissement-RASS.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-JDV-J129-CategorieEtablissement-RASS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="653">
   <si>
     <t>Property</t>
   </si>
@@ -1927,6 +1927,12 @@
   </si>
   <si>
     <t>Centre de santé et de médiation en santé sexuelle</t>
+  </si>
+  <si>
+    <t>650</t>
+  </si>
+  <si>
+    <t>Dispositifs Spécifiques Régionaux en périnatalité</t>
   </si>
   <si>
     <t>695</t>
@@ -2227,7 +2233,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B313"/>
+  <dimension ref="A1:B314"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4727,15 +4733,23 @@
         <v>648</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>650</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B314" t="s" s="2">
+        <v>652</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-FEVRIER-2026/ValueSet-JDV-J129-CategorieEtablissement-RASS.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-JDV-J129-CategorieEtablissement-RASS.xlsx
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
